--- a/sheets/조재수대금교본/검수/찔레꽃.xlsx
+++ b/sheets/조재수대금교본/검수/찔레꽃.xlsx
@@ -4879,7 +4879,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –汰</t>
         </is>
       </c>
@@ -4892,7 +4892,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –汰</t>
         </is>
       </c>
@@ -4928,8 +4928,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -4941,8 +4940,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -4982,8 +4980,7 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -4996,22 +4993,13 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
@@ -5101,47 +5089,19 @@
     </row>
     <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
     </row>
     <row r="9" ht="90.2" customHeight="true">
@@ -5176,15 +5136,13 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -5358,11 +5316,7 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -5371,11 +5325,7 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
@@ -5391,11 +5341,7 @@
         </is>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
     </row>
     <row r="15" ht="6.0" customHeight="true">
@@ -5437,8 +5383,7 @@
       <c r="G17" s="22"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞∼
-‹</t>
+          <t xml:space="preserve">㳞∼</t>
         </is>
       </c>
       <c r="I17" s="22"/>
@@ -5470,7 +5415,7 @@
       <c r="E18" s="23"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅂ∼</t>
+          <t xml:space="preserve">淋∼</t>
         </is>
       </c>
       <c r="G18" s="23"/>
@@ -5504,37 +5449,29 @@
       <c r="F19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="I19" s="24"/>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J19" s="21"/>
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="M19" s="24"/>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O19" s="24"/>
@@ -5614,26 +5551,13 @@
       <c r="C22" s="24"/>
       <c r="D22" s="21"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ
-‹</t>
-        </is>
-      </c>
+      <c r="F22" s="21"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
       <c r="J22" s="21"/>
       <c r="K22" s="24"/>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L22" s="21"/>
       <c r="M22" s="24"/>
       <c r="N22" s="21"/>
       <c r="O22" s="24"/>
@@ -5653,16 +5577,11 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∼
-‹</t>
+          <t xml:space="preserve">淋∼</t>
         </is>
       </c>
       <c r="I23" s="22"/>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J23" s="21"/>
       <c r="K23" s="22"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
@@ -5671,11 +5590,7 @@
         </is>
       </c>
       <c r="M23" s="22"/>
-      <c r="N23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N23" s="21"/>
       <c r="O23" s="22"/>
     </row>
     <row r="24" ht="90.2" customHeight="true">
@@ -5722,30 +5637,26 @@
       <c r="H25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="M25" s="24"/>
       <c r="N25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O25" s="24"/>
@@ -5791,11 +5702,7 @@
       <c r="C27" s="23"/>
       <c r="D27" s="21"/>
       <c r="E27" s="23"/>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ</t>
-        </is>
-      </c>
+      <c r="F27" s="21"/>
       <c r="G27" s="23"/>
       <c r="H27" s="21"/>
       <c r="I27" s="23"/>
@@ -5818,29 +5725,13 @@
         </is>
       </c>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/찔레꽃.xlsx
+++ b/sheets/조재수대금교본/검수/찔레꽃.xlsx
@@ -4879,7 +4879,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –汰</t>
         </is>
       </c>
@@ -4892,7 +4892,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –汰</t>
         </is>
       </c>
@@ -5136,13 +5136,15 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+ﾉ</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+ﾉ</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -5415,7 +5417,7 @@
       <c r="E18" s="23"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∼</t>
+          <t xml:space="preserve">淋ㅂ∼</t>
         </is>
       </c>
       <c r="G18" s="23"/>
@@ -5551,7 +5553,11 @@
       <c r="C22" s="24"/>
       <c r="D22" s="21"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="21"/>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="G22" s="24"/>
       <c r="H22" s="21"/>
       <c r="I22" s="24"/>
@@ -5643,7 +5649,8 @@
       <c r="I25" s="24"/>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="K25" s="24"/>
@@ -5656,7 +5663,8 @@
       <c r="M25" s="24"/>
       <c r="N25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="O25" s="24"/>
@@ -5702,7 +5710,11 @@
       <c r="C27" s="23"/>
       <c r="D27" s="21"/>
       <c r="E27" s="23"/>
-      <c r="F27" s="21"/>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="G27" s="23"/>
       <c r="H27" s="21"/>
       <c r="I27" s="23"/>

--- a/sheets/조재수대금교본/검수/찔레꽃.xlsx
+++ b/sheets/조재수대금교본/검수/찔레꽃.xlsx
@@ -4835,26 +4835,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="65.57" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="97.63" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="97.63" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="97.63" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="97.63" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="97.63" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="97.63" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -5104,7 +5104,7 @@
       <c r="N8" s="21"/>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="97.63" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="97.63" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="97.63" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="97.63" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="97.63" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="97.63" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="65.57" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="97.63" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O17" s="22"/>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="97.63" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="O18" s="23"/>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="97.63" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="O19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="97.63" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="O20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="97.63" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5547,7 +5547,7 @@
       <c r="N21" s="21"/>
       <c r="O21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="97.63" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5568,7 +5568,7 @@
       <c r="N22" s="21"/>
       <c r="O22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="97.63" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5599,7 +5599,7 @@
       <c r="N23" s="21"/>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="97.63" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="O24" s="23"/>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="97.63" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="O25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="97.63" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="O26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="97.63" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5725,7 +5725,7 @@
       <c r="N27" s="21"/>
       <c r="O27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="97.63" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5753,7 +5753,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
